--- a/Stuecklisten/Stueckliste_Elektrobox.xlsx
+++ b/Stuecklisten/Stueckliste_Elektrobox.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\HTL_Bulme\SPL_Project_Watermelon\CandyMachine_Watermelon\Stuecklisten\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HTL\SPL\CandyMaschine_Project\CandyMachine_Watermelon\Stuecklisten\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE24B12C-F74E-4304-9E36-188ED1004702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FCA0376-36B5-4024-B517-92205259C1D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{89EA959D-B92B-42F9-9CA3-2FA253C64293}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{89EA959D-B92B-42F9-9CA3-2FA253C64293}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="87">
   <si>
     <t>Elektrobox:</t>
   </si>
@@ -285,6 +285,18 @@
   </si>
   <si>
     <t>Sechskantmuttern</t>
+  </si>
+  <si>
+    <t>https://www.reichelt.at/at/de/shop/produkt/distanzhuelsen_metall_6-kant_m3_12mm-44788#closemodal</t>
+  </si>
+  <si>
+    <t>https://cdn-reichelt.de/documents/datenblatt/C700/DA12MM_DATENBLAT.pdf</t>
+  </si>
+  <si>
+    <t>Distanzschraube M3</t>
+  </si>
+  <si>
+    <t>Distanzhülsen, Metall, 6-Kant, M3, 12mm</t>
   </si>
 </sst>
 </file>
@@ -294,7 +306,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -337,6 +349,12 @@
     <font>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -385,7 +403,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -418,6 +436,10 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -779,18 +801,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A31737D1-47CA-442F-8EA3-0AF4D09E7E50}">
   <dimension ref="A3:AL68"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.36328125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="55.36328125" customWidth="1"/>
-    <col min="2" max="2" width="62.6328125" customWidth="1"/>
-    <col min="3" max="3" width="30.36328125" customWidth="1"/>
+    <col min="1" max="1" width="55.33203125" customWidth="1"/>
+    <col min="2" max="2" width="62.6640625" customWidth="1"/>
+    <col min="3" max="3" width="30.33203125" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="14.81640625" customWidth="1"/>
-    <col min="6" max="6" width="66.08984375" customWidth="1"/>
-    <col min="7" max="7" width="12.81640625" customWidth="1"/>
+    <col min="5" max="5" width="14.77734375" customWidth="1"/>
+    <col min="6" max="6" width="66.109375" customWidth="1"/>
+    <col min="7" max="7" width="12.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>0</v>
       </c>
@@ -798,7 +820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="2" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" s="2" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -821,7 +843,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -845,7 +867,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -869,7 +891,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>17</v>
       </c>
@@ -893,7 +915,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -916,7 +938,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -940,7 +962,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -964,7 +986,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -988,7 +1010,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -1011,7 +1033,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -1035,7 +1057,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -1058,7 +1080,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>45</v>
       </c>
@@ -1080,7 +1102,7 @@
       </c>
       <c r="G15" s="5"/>
     </row>
-    <row r="16" spans="1:7" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>48</v>
       </c>
@@ -1104,7 +1126,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>51</v>
       </c>
@@ -1127,7 +1149,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="18" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>56</v>
       </c>
@@ -1150,7 +1172,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="19" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>61</v>
       </c>
@@ -1173,7 +1195,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="20" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>66</v>
       </c>
@@ -1185,7 +1207,7 @@
       </c>
       <c r="G20" s="1"/>
     </row>
-    <row r="21" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>69</v>
       </c>
@@ -1208,7 +1230,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="22" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>73</v>
       </c>
@@ -1231,7 +1253,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="23" spans="1:38" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:38" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>78</v>
       </c>
@@ -1255,7 +1277,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="24" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>82</v>
       </c>
@@ -1264,7 +1286,31 @@
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="1:38" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>85</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25">
+        <v>4</v>
+      </c>
+      <c r="D25">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="E25">
+        <f>C25*D25</f>
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="F25" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="G25" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="27" spans="1:38" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="9"/>
       <c r="B27" s="9"/>
       <c r="C27" s="9"/>
@@ -1304,42 +1350,42 @@
       <c r="AK27"/>
       <c r="AL27"/>
     </row>
-    <row r="28" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E28" s="10"/>
       <c r="F28" s="11"/>
       <c r="G28" s="12"/>
     </row>
-    <row r="29" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F29" s="11"/>
       <c r="G29" s="12"/>
     </row>
-    <row r="30" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E30" s="10"/>
       <c r="F30" s="13"/>
       <c r="G30" s="12"/>
     </row>
-    <row r="31" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E31" s="10"/>
       <c r="F31" s="13"/>
       <c r="G31" s="12"/>
     </row>
-    <row r="32" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="8"/>
       <c r="E32" s="14"/>
       <c r="F32" s="11"/>
       <c r="G32" s="12"/>
     </row>
-    <row r="33" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E33" s="10"/>
       <c r="F33" s="12"/>
       <c r="G33" s="12"/>
     </row>
-    <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E34" s="10"/>
       <c r="F34" s="12"/>
       <c r="G34" s="12"/>
     </row>
-    <row r="40" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="9"/>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
@@ -1347,28 +1393,28 @@
       <c r="E40" s="9"/>
       <c r="G40" s="9"/>
     </row>
-    <row r="41" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D41" s="15"/>
       <c r="E41" s="15"/>
       <c r="F41" s="12"/>
       <c r="G41" s="12"/>
     </row>
-    <row r="42" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D42" s="15"/>
       <c r="E42" s="15"/>
       <c r="G42" s="16"/>
     </row>
-    <row r="43" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D43" s="15"/>
       <c r="E43" s="15"/>
       <c r="G43" s="16"/>
     </row>
-    <row r="44" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D44" s="15"/>
       <c r="E44" s="15"/>
       <c r="G44" s="16"/>
     </row>
-    <row r="49" spans="1:38" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:38" s="2" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49"/>
       <c r="B49"/>
       <c r="C49"/>
@@ -1408,49 +1454,49 @@
       <c r="AK49"/>
       <c r="AL49"/>
     </row>
-    <row r="55" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F55" s="12"/>
       <c r="G55" s="12"/>
     </row>
-    <row r="56" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G56" s="12"/>
     </row>
-    <row r="57" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="G57" s="12"/>
     </row>
-    <row r="58" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F58" s="12"/>
     </row>
-    <row r="61" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F61" s="12"/>
       <c r="G61" s="12"/>
     </row>
-    <row r="62" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="E62" s="10"/>
       <c r="F62" s="11"/>
       <c r="G62" s="12"/>
     </row>
-    <row r="63" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F63" s="12"/>
       <c r="G63" s="12"/>
     </row>
-    <row r="64" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:38" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F64" s="12"/>
       <c r="G64" s="12"/>
     </row>
-    <row r="65" spans="4:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="4:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F65" s="12"/>
       <c r="G65" s="12"/>
     </row>
-    <row r="66" spans="4:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="4:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F66" s="12"/>
       <c r="G66" s="12"/>
     </row>
-    <row r="67" spans="4:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="4:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="F67" s="12"/>
       <c r="G67" s="12"/>
     </row>
-    <row r="68" spans="4:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="4:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D68" s="17"/>
       <c r="F68" s="12"/>
       <c r="G68" s="12"/>
@@ -1488,10 +1534,11 @@
     <hyperlink ref="F6" r:id="rId29" xr:uid="{C45E208C-E398-4A90-A279-5567781521DF}"/>
     <hyperlink ref="G16" r:id="rId30" display="https://www.digikey.at/de/products/detail/cvilux-usa/CI0604P1V00-NH/25320625?gclid=4cdf2c11b88d10b6cde645d3d5cc2080&amp;gclsrc=3p.ds&amp;&amp;utm_adgroup=&amp;utm_source=bing&amp;utm_medium=cpc&amp;utm_campaign=PMax%20Shopping_Product_High%20ROAS&amp;utm_term=&amp;productid=25320625&amp;utm_content=&amp;utm_id=bi_cmp-627379374_adg-1298524459035859_ad-81157838939736_pla-2332957516180621_dev-c_ext-_prd-25320625&amp;msclkid=4cdf2c11b88d10b6cde645d3d5cc2080" xr:uid="{9BF8DAB6-D949-4805-9862-891877906466}"/>
     <hyperlink ref="F16" r:id="rId31" display="https://www.digikey.at/de/products/detail/cvilux-usa/CI0604P1V00-NH/25320625?gclid=4cdf2c11b88d10b6cde645d3d5cc2080&amp;gclsrc=3p.ds&amp;&amp;utm_adgroup=&amp;utm_source=bing&amp;utm_medium=cpc&amp;utm_campaign=PMax%20Shopping_Product_High%20ROAS&amp;utm_term=&amp;productid=25320625&amp;utm_content=&amp;utm_id=bi_cmp-627379374_adg-1298524459035859_ad-81157838939736_pla-2332957516180621_dev-c_ext-_prd-25320625&amp;msclkid=4cdf2c11b88d10b6cde645d3d5cc2080" xr:uid="{183540FB-EC0D-4B32-AE7E-84EE5D8B6F42}"/>
+    <hyperlink ref="F25" r:id="rId32" xr:uid="{E48C93B0-5A7E-4B4E-9475-88E3440D3A90}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId32"/>
+    <tablePart r:id="rId33"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1508,15 +1555,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100B6182DFB92986B40983C102328C5D723" ma:contentTypeVersion="10" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="4c3a62a0b7c37ad92c234a8575bb4c81">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="80e0ce60-6d73-4f22-8efa-583dd61b38a6" xmlns:ns3="6b80be42-7ea9-4824-bca4-1af6e9998e40" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="378231f9db0de1fb5ff8ac0a4788cbcf" ns2:_="" ns3:_="">
     <xsd:import namespace="80e0ce60-6d73-4f22-8efa-583dd61b38a6"/>
@@ -1705,6 +1743,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB6BC598-5F69-48F8-A3B9-E9DBAA18F232}">
   <ds:schemaRefs>
@@ -1717,14 +1764,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E92FA24D-1929-465D-B9B2-50D69E4F4517}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F7FEE953-ACA5-4A42-8F93-D6995045B27A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1741,4 +1780,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E92FA24D-1929-465D-B9B2-50D69E4F4517}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>